--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,6 +319,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:code</t>
   </si>
   <si>
@@ -363,9 +366,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:code.value[x]</t>
@@ -1190,24 +1190,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1232,10 +1232,10 @@
         <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1295,7 +1295,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1441,7 +1441,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1501,7 +1501,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>81</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1538,16 +1538,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1597,7 +1597,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>83</v>
@@ -1612,7 +1612,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -1707,13 +1707,13 @@
         <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -1752,7 +1752,7 @@
         <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1812,7 +1812,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>81</v>
@@ -1826,7 +1826,7 @@
         <v>127</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1929,7 +1929,7 @@
         <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2018,7 +2018,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>81</v>
@@ -2032,7 +2032,7 @@
         <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2055,16 +2055,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2114,7 +2114,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>83</v>
@@ -2129,7 +2129,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2226,21 +2226,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2263,16 +2263,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2322,7 +2322,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -2337,7 +2337,7 @@
         <v>76</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -2434,13 +2434,13 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>123</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-ext-person-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
